--- a/stats for com eng/excel files/Ch06-01.xlsx
+++ b/stats for com eng/excel files/Ch06-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pin/Desktop/joint-repository/stats for com eng/excel files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE66AB0-05E7-AC41-A18E-C9A794EF447A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14798386-4061-FF4C-874A-31389E542609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="24080" windowHeight="13160" xr2:uid="{0900C177-0103-404A-B722-511C268DDC47}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="20480" windowHeight="11000" xr2:uid="{0900C177-0103-404A-B722-511C268DDC47}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Observation Number</t>
   </si>
@@ -195,16 +195,70 @@
   <si>
     <t>t(alpha/2), use positive side because we want to get positive value</t>
   </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>activity</t>
+  </si>
+  <si>
+    <t>y is activity</t>
+  </si>
+  <si>
+    <t>y is time</t>
+  </si>
+  <si>
+    <t>y is time, x is activity</t>
+  </si>
+  <si>
+    <t>Xi - Xbar</t>
+  </si>
+  <si>
+    <t>Yi - Ybar</t>
+  </si>
+  <si>
+    <t>Xbar</t>
+  </si>
+  <si>
+    <t>Ybar</t>
+  </si>
+  <si>
+    <t>Sxx</t>
+  </si>
+  <si>
+    <t>Sxy</t>
+  </si>
+  <si>
+    <t>(Xi-Xbar)(Yi-Ybar)</t>
+  </si>
+  <si>
+    <t>Beta1</t>
+  </si>
+  <si>
+    <t>Beta0</t>
+  </si>
+  <si>
+    <t>y=106.2-11.4*x</t>
+  </si>
+  <si>
+    <t>y=9.218-0.086*x</t>
+  </si>
+  <si>
+    <t>x=80</t>
+  </si>
+  <si>
+    <t>x=0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="178" formatCode="0.000000"/>
-    <numFmt numFmtId="179" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +284,13 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri (Body)"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -331,13 +392,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2690,13 +2751,13 @@
       <c r="J23" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="19" t="s">
+      <c r="K23" s="13" t="s">
         <v>38</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="N23" s="20">
+      <c r="N23" s="19">
         <f>K24/(COUNT(A2:A21)-2)</f>
         <v>1.1805457222222246</v>
       </c>
@@ -2853,10 +2914,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77C267C-F4BC-4234-89D0-A1B722677F09}">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
@@ -2876,7 +2937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -2895,20 +2956,407 @@
       <c r="F2" s="6">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K2" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="V2" s="20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>96</v>
+      </c>
+      <c r="K3">
+        <f>I3-$I$9</f>
+        <v>-2</v>
+      </c>
+      <c r="L3">
+        <f>J3-$J$9</f>
+        <v>24</v>
+      </c>
+      <c r="M3">
+        <f>K3^2</f>
+        <v>4</v>
+      </c>
+      <c r="N3">
+        <f>K3*L3</f>
+        <v>-48</v>
+      </c>
+      <c r="Q3" s="20">
+        <v>96</v>
+      </c>
+      <c r="R3" s="20">
+        <v>1</v>
+      </c>
+      <c r="S3" s="20">
+        <v>24</v>
+      </c>
+      <c r="T3" s="20">
+        <v>-2</v>
+      </c>
+      <c r="U3">
+        <f>S3^2</f>
+        <v>576</v>
+      </c>
+      <c r="V3" s="20">
+        <v>-48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>84</v>
+      </c>
+      <c r="K4">
+        <f t="shared" ref="K4:K8" si="0">I4-$I$9</f>
+        <v>-1</v>
+      </c>
+      <c r="L4">
+        <f t="shared" ref="L4:L8" si="1">J4-$J$9</f>
+        <v>12</v>
+      </c>
+      <c r="M4">
+        <f t="shared" ref="M4:M8" si="2">K4^2</f>
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <f t="shared" ref="N4:N7" si="3">K4*L4</f>
+        <v>-12</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>84</v>
+      </c>
+      <c r="R4" s="20">
+        <v>2</v>
+      </c>
+      <c r="S4" s="20">
+        <v>12</v>
+      </c>
+      <c r="T4" s="20">
+        <v>-1</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U7" si="4">S4^2</f>
+        <v>144</v>
+      </c>
+      <c r="V4" s="20">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <v>70</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="1"/>
+        <v>-2</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>70</v>
+      </c>
+      <c r="R5" s="20">
+        <v>3</v>
+      </c>
+      <c r="S5" s="20">
+        <v>-2</v>
+      </c>
+      <c r="T5" s="20">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="V5" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>58</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="1"/>
+        <v>-14</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="3"/>
+        <v>-14</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>58</v>
+      </c>
+      <c r="R6" s="20">
+        <v>4</v>
+      </c>
+      <c r="S6" s="20">
+        <v>-14</v>
+      </c>
+      <c r="T6" s="20">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>196</v>
+      </c>
+      <c r="V6" s="20">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>52</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="1"/>
+        <v>-20</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="3"/>
+        <v>-40</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>52</v>
+      </c>
+      <c r="R7" s="20">
+        <v>5</v>
+      </c>
+      <c r="S7" s="20">
+        <v>-20</v>
+      </c>
+      <c r="T7" s="20">
+        <v>2</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>400</v>
+      </c>
+      <c r="V7" s="20">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>48</v>
+      </c>
+      <c r="R8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U8" t="s">
+        <v>50</v>
+      </c>
+      <c r="V8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <f>AVERAGE(I3:I7)</f>
+        <v>3</v>
+      </c>
+      <c r="J9">
+        <f>AVERAGE(J3:J7)</f>
+        <v>72</v>
+      </c>
+      <c r="M9">
+        <f>SUM(M3:M7)</f>
+        <v>10</v>
+      </c>
+      <c r="N9">
+        <f>SUM(N3:N7)</f>
+        <v>-114</v>
+      </c>
+      <c r="Q9">
+        <f>AVERAGE(Q3:Q7)</f>
+        <v>72</v>
+      </c>
+      <c r="R9">
+        <f>AVERAGE(R3:R7)</f>
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <f>SUM(U3:U7)</f>
+        <v>1320</v>
+      </c>
+      <c r="V9">
+        <f>SUM(V3:V7)</f>
+        <v>-114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R10" t="s">
+        <v>53</v>
+      </c>
+      <c r="S10">
+        <f>V9/U9</f>
+        <v>-8.6363636363636365E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" t="s">
+        <v>53</v>
+      </c>
+      <c r="L11">
+        <f>N9/M9</f>
+        <v>-11.4</v>
+      </c>
+      <c r="N11" t="s">
+        <v>55</v>
+      </c>
+      <c r="R11" t="s">
+        <v>54</v>
+      </c>
+      <c r="S11">
+        <f>R9-S10*Q9</f>
+        <v>9.2181818181818187</v>
+      </c>
+      <c r="U11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K12" t="s">
+        <v>54</v>
+      </c>
+      <c r="L12">
+        <f>J9-L11*I9</f>
+        <v>106.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16">
+        <f>9.218-0.086*80</f>
+        <v>2.338000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <f>9.218-0.086*0</f>
+        <v>9.218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
